--- a/02_AI_Strategy_and_Roadmap/GT_AI_Strategy_Toolkit.xlsx
+++ b/02_AI_Strategy_and_Roadmap/GT_AI_Strategy_Toolkit.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -13,8 +12,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Roadmap (Gantt)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. KPI Tracker" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Ready7 Traceability" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. AI Apps Pipeline" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Guide'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'1. SWOT &amp; TOWS'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2. Use-Case Scoring'!$A$1:$R$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'3. Roadmap (Gantt)'!$A$1:$Z$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'4. KPI Tracker'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'5. Ready7 Traceability'!$A$1:$F$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'6. AI Apps Pipeline'!$A$1:$H$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -732,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -817,10 +825,22 @@
     <row r="9" ht="32" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>6. AI Apps Pipeline</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Status of GT AI tools and apps, incl. the AI-powered BCP and Financial Statements tools (in preparation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>Colour legend</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Yellow = input  |  Purple = header / calculated</t>
         </is>
@@ -831,8 +851,9 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -941,7 +962,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Four defined AI service lines and proprietary tools (RCM v2.0, risk framework, readiness tool)</t>
+          <t>Four AI service lines, proprietary tools (RCM v2.1, risk framework, readiness tool, security audit checklist) and two AI apps in preparation (BCP, Financial Statements)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1105,8 +1126,9 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2166,8 +2188,9 @@
       <formula1>"Low,Medium,High,Critical"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2178,7 +2201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3258,7 +3281,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>WS5 AI Service Line (GTM)</t>
+          <t>WS5 AI Service Line &amp; Apps</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -3308,19 +3331,19 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>WS5 AI Service Line (GTM)</t>
+          <t>WS5 AI Service Line &amp; Apps</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Launch &amp; first pilot clients</t>
+          <t>AI apps (BCP, Financial Statements): design &amp; MVP</t>
         </is>
       </c>
       <c r="C23" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="28">
         <f>INDEX($H$4:$Y$4,MIN(18,C23+D23-1))</f>
@@ -3358,16 +3381,16 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>WS5 AI Service Line (GTM)</t>
+          <t>WS5 AI Service Line &amp; Apps</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Sector campaigns (FS, government, telecom)</t>
+          <t>AI apps: risk assessment, internal pilot &amp; client launch</t>
         </is>
       </c>
       <c r="C24" s="20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="20" t="n">
         <v>7</v>
@@ -3408,19 +3431,19 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>WS5 AI Service Line (GTM)</t>
+          <t>WS5 AI Service Line &amp; Apps</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Regional scale via the GT network</t>
+          <t>Launch &amp; first pilot clients</t>
         </is>
       </c>
       <c r="C25" s="20" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D25" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="28">
         <f>INDEX($H$4:$Y$4,MIN(18,C25+D25-1))</f>
@@ -3455,12 +3478,112 @@
       <c r="X25" s="30" t="n"/>
       <c r="Y25" s="30" t="n"/>
     </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>WS5 AI Service Line &amp; Apps</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>Sector campaigns (FS, government, telecom)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="28">
+        <f>INDEX($H$4:$Y$4,MIN(18,C26+D26-1))</f>
+        <v/>
+      </c>
+      <c r="F26" s="29" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="n"/>
+      <c r="I26" s="30" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
+      <c r="M26" s="30" t="n"/>
+      <c r="N26" s="31" t="n"/>
+      <c r="O26" s="30" t="n"/>
+      <c r="P26" s="30" t="n"/>
+      <c r="Q26" s="30" t="n"/>
+      <c r="R26" s="30" t="n"/>
+      <c r="S26" s="30" t="n"/>
+      <c r="T26" s="30" t="n"/>
+      <c r="U26" s="30" t="n"/>
+      <c r="V26" s="30" t="n"/>
+      <c r="W26" s="31" t="n"/>
+      <c r="X26" s="30" t="n"/>
+      <c r="Y26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>WS5 AI Service Line &amp; Apps</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Regional scale via the GT network</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="28">
+        <f>INDEX($H$4:$Y$4,MIN(18,C27+D27-1))</f>
+        <v/>
+      </c>
+      <c r="F27" s="29" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H27" s="30" t="n"/>
+      <c r="I27" s="30" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
+      <c r="M27" s="30" t="n"/>
+      <c r="N27" s="31" t="n"/>
+      <c r="O27" s="30" t="n"/>
+      <c r="P27" s="30" t="n"/>
+      <c r="Q27" s="30" t="n"/>
+      <c r="R27" s="30" t="n"/>
+      <c r="S27" s="30" t="n"/>
+      <c r="T27" s="30" t="n"/>
+      <c r="U27" s="30" t="n"/>
+      <c r="V27" s="30" t="n"/>
+      <c r="W27" s="31" t="n"/>
+      <c r="X27" s="30" t="n"/>
+      <c r="Y27" s="30" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:Y25">
+  <conditionalFormatting sqref="H5:Y27">
     <cfRule type="expression" priority="1" dxfId="7">
       <formula>AND(LEFT($A5,3)="WS1",H$3&gt;=$C5,H$3&lt;$C5+$D5)</formula>
     </cfRule>
@@ -3477,7 +3600,7 @@
       <formula>AND(LEFT($A5,3)="WS5",H$3&gt;=$C5,H$3&lt;$C5+$D5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G25">
+  <conditionalFormatting sqref="G5:G27">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
       <formula>"Delayed"</formula>
     </cfRule>
@@ -3486,12 +3609,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Not started,Planned,In progress,Completed,Delayed"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3502,7 +3626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3784,27 +3908,27 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Client-data leakage incidents via AI</t>
+          <t>GT AI apps (BCP tool, Financial Statements tool)</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 in preparation</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2 piloted with clients</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2 launched commercially</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>CISO / DPO</t>
+          <t>AI service line lead</t>
         </is>
       </c>
       <c r="F12" s="32" t="n"/>
@@ -3814,39 +3938,69 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>ISO/IEC 42001 status</t>
+          <t>Client-data leakage incidents via AI</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Certification-ready</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Certified (optional)</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>Risk &amp; Quality partner</t>
+          <t>CISO / DPO</t>
         </is>
       </c>
       <c r="F13" s="32" t="n"/>
       <c r="G13" s="32" t="n"/>
       <c r="H13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>ISO/IEC 42001 status</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Certification-ready</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Certified (optional)</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Risk &amp; Quality partner</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G13">
+  <conditionalFormatting sqref="G5:G14">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"On track"</formula>
     </cfRule>
@@ -3858,12 +4012,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G5:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"On track,At risk,Off track"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4683,7 +4838,349 @@
       <formula>"Most Met"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004F2D7F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>6. GT AI Apps &amp; Tools Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Status of GT proprietary AI tools and apps. AI-powered BCP tool and AI-powered Financial Statements tool are in preparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tool / app</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Service line</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Next milestone</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Risk tier (GT framework)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>GT AI Readiness &amp; Risk Assessment Tool</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>15-question organisational AI readiness &amp; risk-exposure assessment with auto-generated report</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>AI GRC</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Available (v1.1)</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Client pilots in H1</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="n"/>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>GT AI RCM v2.1 + AI Security &amp; Agent Audit Checklist</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>81-control AI risk &amp; control matrix and 125-item security / agent audit programme</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>AI GRC / Cyber</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>First engagements in H1</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>GT AI Risk Assessment Framework &amp; Toolkit</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Use-case tiering, 52-risk taxonomy, register, heat map and sign-off</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>AI GRC</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Available (v1.1)</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Embed in AI CoE intake</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H7" s="32" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>AI-powered BCP tool</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>AI-assisted business impact analysis, BCP / DR plan drafting and tabletop scenarios</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>AI Automation / Risk Advisory</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>In preparation</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>MVP &amp; internal pilot (indicative H1-H2)</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>AI-powered Financial Statements tool</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>AI-assisted preparation and review of IFRS financial statements and disclosures</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>AI Automation / Accounting Advisory</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>In preparation</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>MVP &amp; internal pilot (indicative H1-H2)</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>Independence check required for audit clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Client AI self-assessment portal</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Web version of the readiness tool for lead generation and delivery</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>AI GRC</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Build in H2</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>AI service line lead</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H10" s="32" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D10">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>LEFT($D5,14)="In preparation"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>LEFT($D5,7)="Planned"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>LEFT($D5,9)="Available"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>LEFT($D5,8)="Launched"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>LEFT($D5,5)="Pilot"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Available,In preparation,Planned,Pilot,Launched,On hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/02_AI_Strategy_and_Roadmap/GT_AI_Strategy_Toolkit.xlsx
+++ b/02_AI_Strategy_and_Roadmap/GT_AI_Strategy_Toolkit.xlsx
@@ -1308,11 +1308,11 @@
       </c>
       <c r="M5" s="16">
         <f>SUM(E5:H5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N5" s="16">
         <f>SUM(I5:L5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O5" s="14" t="inlineStr"/>
       <c r="P5" s="14" t="inlineStr"/>
@@ -1363,19 +1363,19 @@
       </c>
       <c r="M6" s="21">
         <f>ROUND(SUMPRODUCT(E6:H6,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="N6" s="21">
         <f>ROUND(SUMPRODUCT(I6:L6,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O6" s="22">
+        <v>4.5</v>
+      </c>
+      <c r="O6" s="22" t="str">
         <f>IF(AND(M6&gt;=$B$3,N6&gt;=$B$3),"Quick win",IF(M6&gt;=$B$3,"Strategic bet",IF(N6&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Quick win</v>
       </c>
       <c r="P6" s="17">
         <f>RANK(M6+N6+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q6" s="20" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R6">
         <f>M6+N6+ROW()/10000</f>
-        <v/>
+        <v>8.5006</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="M7" s="21">
         <f>ROUND(SUMPRODUCT(E7:H7,$E$5:$H$5),2)</f>
-        <v/>
+        <v>3.15</v>
       </c>
       <c r="N7" s="21">
         <f>ROUND(SUMPRODUCT(I7:L7,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O7" s="22">
+        <v>4.8</v>
+      </c>
+      <c r="O7" s="22" t="str">
         <f>IF(AND(M7&gt;=$B$3,N7&gt;=$B$3),"Quick win",IF(M7&gt;=$B$3,"Strategic bet",IF(N7&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Fill-in</v>
       </c>
       <c r="P7" s="17">
         <f>RANK(M7+N7+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="Q7" s="20" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="R7">
         <f>M7+N7+ROW()/10000</f>
-        <v/>
+        <v>7.9507</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1501,19 +1501,19 @@
       </c>
       <c r="M8" s="21">
         <f>ROUND(SUMPRODUCT(E8:H8,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4.25</v>
       </c>
       <c r="N8" s="21">
         <f>ROUND(SUMPRODUCT(I8:L8,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O8" s="22">
+        <v>3.7</v>
+      </c>
+      <c r="O8" s="22" t="str">
         <f>IF(AND(M8&gt;=$B$3,N8&gt;=$B$3),"Quick win",IF(M8&gt;=$B$3,"Strategic bet",IF(N8&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Quick win</v>
       </c>
       <c r="P8" s="17">
         <f>RANK(M8+N8+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q8" s="20" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="R8">
         <f>M8+N8+ROW()/10000</f>
-        <v/>
+        <v>7.9508</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1570,19 +1570,19 @@
       </c>
       <c r="M9" s="21">
         <f>ROUND(SUMPRODUCT(E9:H9,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4.85</v>
       </c>
       <c r="N9" s="21">
         <f>ROUND(SUMPRODUCT(I9:L9,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O9" s="22">
+        <v>3</v>
+      </c>
+      <c r="O9" s="22" t="str">
         <f>IF(AND(M9&gt;=$B$3,N9&gt;=$B$3),"Quick win",IF(M9&gt;=$B$3,"Strategic bet",IF(N9&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Strategic bet</v>
       </c>
       <c r="P9" s="17">
         <f>RANK(M9+N9+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="Q9" s="20" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="R9">
         <f>M9+N9+ROW()/10000</f>
-        <v/>
+        <v>7.8509</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="M10" s="21">
         <f>ROUND(SUMPRODUCT(E10:H10,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="N10" s="21">
         <f>ROUND(SUMPRODUCT(I10:L10,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O10" s="22">
+        <v>3.7</v>
+      </c>
+      <c r="O10" s="22" t="str">
         <f>IF(AND(M10&gt;=$B$3,N10&gt;=$B$3),"Quick win",IF(M10&gt;=$B$3,"Strategic bet",IF(N10&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Quick win</v>
       </c>
       <c r="P10" s="17">
         <f>RANK(M10+N10+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q10" s="20" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="R10">
         <f>M10+N10+ROW()/10000</f>
-        <v/>
+        <v>7.701</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1708,19 +1708,19 @@
       </c>
       <c r="M11" s="21">
         <f>ROUND(SUMPRODUCT(E11:H11,$E$5:$H$5),2)</f>
-        <v/>
+        <v>3.85</v>
       </c>
       <c r="N11" s="21">
         <f>ROUND(SUMPRODUCT(I11:L11,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O11" s="22">
+        <v>3.25</v>
+      </c>
+      <c r="O11" s="22" t="str">
         <f>IF(AND(M11&gt;=$B$3,N11&gt;=$B$3),"Quick win",IF(M11&gt;=$B$3,"Strategic bet",IF(N11&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Strategic bet</v>
       </c>
       <c r="P11" s="17">
         <f>RANK(M11+N11+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="R11">
         <f>M11+N11+ROW()/10000</f>
-        <v/>
+        <v>7.1011</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -1777,19 +1777,19 @@
       </c>
       <c r="M12" s="21">
         <f>ROUND(SUMPRODUCT(E12:H12,$E$5:$H$5),2)</f>
-        <v/>
+        <v>3.35</v>
       </c>
       <c r="N12" s="21">
         <f>ROUND(SUMPRODUCT(I12:L12,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O12" s="22">
+        <v>3</v>
+      </c>
+      <c r="O12" s="22" t="str">
         <f>IF(AND(M12&gt;=$B$3,N12&gt;=$B$3),"Quick win",IF(M12&gt;=$B$3,"Strategic bet",IF(N12&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Deprioritise</v>
       </c>
       <c r="P12" s="17">
         <f>RANK(M12+N12+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="Q12" s="20" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="R12">
         <f>M12+N12+ROW()/10000</f>
-        <v/>
+        <v>6.3512</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1846,19 +1846,19 @@
       </c>
       <c r="M13" s="21">
         <f>ROUND(SUMPRODUCT(E13:H13,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="N13" s="21">
         <f>ROUND(SUMPRODUCT(I13:L13,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O13" s="22">
+        <v>3.45</v>
+      </c>
+      <c r="O13" s="22" t="str">
         <f>IF(AND(M13&gt;=$B$3,N13&gt;=$B$3),"Quick win",IF(M13&gt;=$B$3,"Strategic bet",IF(N13&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Strategic bet</v>
       </c>
       <c r="P13" s="17">
         <f>RANK(M13+N13+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="R13">
         <f>M13+N13+ROW()/10000</f>
-        <v/>
+        <v>7.4513</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1915,19 +1915,19 @@
       </c>
       <c r="M14" s="21">
         <f>ROUND(SUMPRODUCT(E14:H14,$E$5:$H$5),2)</f>
-        <v/>
+        <v>2.85</v>
       </c>
       <c r="N14" s="21">
         <f>ROUND(SUMPRODUCT(I14:L14,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O14" s="22">
+        <v>4.05</v>
+      </c>
+      <c r="O14" s="22" t="str">
         <f>IF(AND(M14&gt;=$B$3,N14&gt;=$B$3),"Quick win",IF(M14&gt;=$B$3,"Strategic bet",IF(N14&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Fill-in</v>
       </c>
       <c r="P14" s="17">
         <f>RANK(M14+N14+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q14" s="20" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="R14">
         <f>M14+N14+ROW()/10000</f>
-        <v/>
+        <v>6.9014</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1984,19 +1984,19 @@
       </c>
       <c r="M15" s="21">
         <f>ROUND(SUMPRODUCT(E15:H15,$E$5:$H$5),2)</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="N15" s="21">
         <f>ROUND(SUMPRODUCT(I15:L15,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O15" s="22">
+        <v>4.75</v>
+      </c>
+      <c r="O15" s="22" t="str">
         <f>IF(AND(M15&gt;=$B$3,N15&gt;=$B$3),"Quick win",IF(M15&gt;=$B$3,"Strategic bet",IF(N15&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Fill-in</v>
       </c>
       <c r="P15" s="17">
         <f>RANK(M15+N15+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="Q15" s="20" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R15">
         <f>M15+N15+ROW()/10000</f>
-        <v/>
+        <v>7.1515</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="M16" s="21">
         <f>ROUND(SUMPRODUCT(E16:H16,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4.6</v>
       </c>
       <c r="N16" s="21">
         <f>ROUND(SUMPRODUCT(I16:L16,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O16" s="22">
+        <v>2</v>
+      </c>
+      <c r="O16" s="22" t="str">
         <f>IF(AND(M16&gt;=$B$3,N16&gt;=$B$3),"Quick win",IF(M16&gt;=$B$3,"Strategic bet",IF(N16&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Strategic bet</v>
       </c>
       <c r="P16" s="17">
         <f>RANK(M16+N16+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="Q16" s="20" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="R16">
         <f>M16+N16+ROW()/10000</f>
-        <v/>
+        <v>6.6016</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2122,19 +2122,19 @@
       </c>
       <c r="M17" s="21">
         <f>ROUND(SUMPRODUCT(E17:H17,$E$5:$H$5),2)</f>
-        <v/>
+        <v>4.4</v>
       </c>
       <c r="N17" s="21">
         <f>ROUND(SUMPRODUCT(I17:L17,$I$5:$L$5),2)</f>
-        <v/>
-      </c>
-      <c r="O17" s="22">
+        <v>3.2</v>
+      </c>
+      <c r="O17" s="22" t="str">
         <f>IF(AND(M17&gt;=$B$3,N17&gt;=$B$3),"Quick win",IF(M17&gt;=$B$3,"Strategic bet",IF(N17&gt;=$B$3,"Fill-in","Deprioritise")))</f>
-        <v/>
+        <v>Strategic bet</v>
       </c>
       <c r="P17" s="17">
         <f>RANK(M17+N17+ROW()/10000,$R$6:$R$17)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="Q17" s="20" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="R17">
         <f>M17+N17+ROW()/10000</f>
-        <v/>
+        <v>7.6017</v>
       </c>
     </row>
   </sheetData>
@@ -2445,9 +2445,9 @@
       <c r="D5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C5+D5-1))</f>
-        <v/>
+        <v>Nov-26</v>
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
@@ -2495,9 +2495,9 @@
       <c r="D6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C6+D6-1))</f>
-        <v/>
+        <v>Nov-26</v>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
@@ -2545,9 +2545,9 @@
       <c r="D7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C7+D7-1))</f>
-        <v/>
+        <v>Feb-27</v>
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
@@ -2595,9 +2595,9 @@
       <c r="D8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C8+D8-1))</f>
-        <v/>
+        <v>Mar-27</v>
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
@@ -2645,9 +2645,9 @@
       <c r="D9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C9+D9-1))</f>
-        <v/>
+        <v>Oct-27</v>
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
@@ -2695,9 +2695,9 @@
       <c r="D10" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C10+D10-1))</f>
-        <v/>
+        <v>Jan-28</v>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
@@ -2745,9 +2745,9 @@
       <c r="D11" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C11+D11-1))</f>
-        <v/>
+        <v>Mar-27</v>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
@@ -2795,9 +2795,9 @@
       <c r="D12" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C12+D12-1))</f>
-        <v/>
+        <v>Aug-27</v>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
@@ -2845,9 +2845,9 @@
       <c r="D13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C13+D13-1))</f>
-        <v/>
+        <v>Sep-27</v>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
@@ -2895,9 +2895,9 @@
       <c r="D14" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C14+D14-1))</f>
-        <v/>
+        <v>Mar-28</v>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
@@ -2945,9 +2945,9 @@
       <c r="D15" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C15+D15-1))</f>
-        <v/>
+        <v>Jan-27</v>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
@@ -2995,9 +2995,9 @@
       <c r="D16" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C16+D16-1))</f>
-        <v/>
+        <v>Apr-27</v>
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
@@ -3045,9 +3045,9 @@
       <c r="D17" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C17+D17-1))</f>
-        <v/>
+        <v>Jun-27</v>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
@@ -3095,9 +3095,9 @@
       <c r="D18" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C18+D18-1))</f>
-        <v/>
+        <v>Oct-27</v>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
@@ -3145,9 +3145,9 @@
       <c r="D19" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C19+D19-1))</f>
-        <v/>
+        <v>Mar-27</v>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
@@ -3195,9 +3195,9 @@
       <c r="D20" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C20+D20-1))</f>
-        <v/>
+        <v>Aug-27</v>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
@@ -3245,9 +3245,9 @@
       <c r="D21" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C21+D21-1))</f>
-        <v/>
+        <v>Mar-28</v>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
@@ -3295,9 +3295,9 @@
       <c r="D22" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C22+D22-1))</f>
-        <v/>
+        <v>Dec-26</v>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
@@ -3345,9 +3345,9 @@
       <c r="D23" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C23+D23-1))</f>
-        <v/>
+        <v>Apr-27</v>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
@@ -3395,9 +3395,9 @@
       <c r="D24" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C24+D24-1))</f>
-        <v/>
+        <v>Nov-27</v>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
@@ -3445,9 +3445,9 @@
       <c r="D25" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C25+D25-1))</f>
-        <v/>
+        <v>Apr-27</v>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
@@ -3495,9 +3495,9 @@
       <c r="D26" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C26+D26-1))</f>
-        <v/>
+        <v>Oct-27</v>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
@@ -3545,9 +3545,9 @@
       <c r="D27" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="28" t="str">
         <f>INDEX($H$4:$Y$4,MIN(18,C27+D27-1))</f>
-        <v/>
+        <v>Mar-28</v>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
